--- a/readme/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
+++ b/readme/ig/CdaRTO-PQ-PQToRatioConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T12:13:45+00:00</t>
+    <t>2026-07-17T13:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
